--- a/AAAGameData/DataTables/DamageFloatingTextTable.xlsx
+++ b/AAAGameData/DataTables/DamageFloatingTextTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1316,7 +1316,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1563,7 +1563,7 @@
         <v>1.5</v>
       </c>
       <c r="M5" s="1">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="1">
         <v>0.2</v>
@@ -1617,7 +1617,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="1">
-        <v>80</v>
+        <v>0.8</v>
       </c>
       <c r="N6" s="1">
         <v>0.3</v>
@@ -1671,7 +1671,7 @@
         <v>1.8</v>
       </c>
       <c r="M7" s="1">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="N7" s="1">
         <v>0.25</v>
@@ -1725,7 +1725,7 @@
         <v>2.2</v>
       </c>
       <c r="M8" s="1">
-        <v>70</v>
+        <v>0.7</v>
       </c>
       <c r="N8" s="1">
         <v>0.3</v>
@@ -1779,7 +1779,7 @@
         <v>1.2</v>
       </c>
       <c r="M9" s="1">
-        <v>40</v>
+        <v>0.4</v>
       </c>
       <c r="N9" s="1">
         <v>0.2</v>
@@ -1833,7 +1833,7 @@
         <v>2.5</v>
       </c>
       <c r="M10" s="1">
-        <v>55</v>
+        <v>0.55</v>
       </c>
       <c r="N10" s="1">
         <v>0.25</v>
@@ -1887,7 +1887,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="1">
-        <v>65</v>
+        <v>0.65</v>
       </c>
       <c r="N11" s="1">
         <v>0.3</v>
@@ -1941,7 +1941,7 @@
         <v>2.2</v>
       </c>
       <c r="M12" s="1">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="N12" s="1">
         <v>0.25</v>
@@ -1995,7 +1995,7 @@
         <v>1.8</v>
       </c>
       <c r="M13" s="1">
-        <v>75</v>
+        <v>0.75</v>
       </c>
       <c r="N13" s="1">
         <v>0.2</v>
@@ -2049,7 +2049,7 @@
         <v>2</v>
       </c>
       <c r="M14" s="1">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="N14" s="1">
         <v>0.3</v>
@@ -2103,7 +2103,7 @@
         <v>1.8</v>
       </c>
       <c r="M15" s="1">
-        <v>45</v>
+        <v>0.45</v>
       </c>
       <c r="N15" s="1">
         <v>0.25</v>
@@ -2157,7 +2157,7 @@
         <v>1.5</v>
       </c>
       <c r="M16" s="1">
-        <v>40</v>
+        <v>0.4</v>
       </c>
       <c r="N16" s="1">
         <v>0.2</v>
@@ -2211,7 +2211,7 @@
         <v>1.8</v>
       </c>
       <c r="M17" s="1">
-        <v>45</v>
+        <v>0.45</v>
       </c>
       <c r="N17" s="1">
         <v>0.25</v>
@@ -2265,7 +2265,7 @@
         <v>2.5</v>
       </c>
       <c r="M18" s="1">
-        <v>85</v>
+        <v>0.85</v>
       </c>
       <c r="N18" s="1">
         <v>0.3</v>
@@ -2319,7 +2319,7 @@
         <v>2</v>
       </c>
       <c r="M19" s="1">
-        <v>70</v>
+        <v>0.7</v>
       </c>
       <c r="N19" s="1">
         <v>0.25</v>
@@ -2373,7 +2373,7 @@
         <v>1.8</v>
       </c>
       <c r="M20" s="1">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="N20" s="1">
         <v>0.2</v>
@@ -2427,7 +2427,7 @@
         <v>2.2</v>
       </c>
       <c r="M21" s="1">
-        <v>55</v>
+        <v>0.55</v>
       </c>
       <c r="N21" s="1">
         <v>0.3</v>
@@ -2481,7 +2481,7 @@
         <v>1.5</v>
       </c>
       <c r="M22" s="1">
-        <v>35</v>
+        <v>0.35</v>
       </c>
       <c r="N22" s="1">
         <v>0.2</v>
@@ -2535,7 +2535,7 @@
         <v>1.8</v>
       </c>
       <c r="M23" s="1">
-        <v>40</v>
+        <v>0.4</v>
       </c>
       <c r="N23" s="1">
         <v>0.25</v>
@@ -2589,7 +2589,7 @@
         <v>1.5</v>
       </c>
       <c r="M24" s="1">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="N24" s="1">
         <v>0.2</v>
